--- a/data/trans_orig/IP07_A11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A11_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2956</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2574</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10875</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1389</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6086</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7931</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26619</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9437</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16855</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10799</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62955</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54005</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69789</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>47626</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41012</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52016</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>51200</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74454</t>
+          <t>56234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>112670</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96926</t>
+          <t>103967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123180</t>
+          <t>122891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6943</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3028</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14356</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3978</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8274</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4242</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21437</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6871</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12839</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122993</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>112095</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130611</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>82029</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75041</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87924</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>125167</t>
+          <t>87639</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116462</t>
+          <t>79902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133678</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>210632</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195721</t>
+          <t>197143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216374</t>
+          <t>220260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5847</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5735</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8015</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26313</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10182</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11405</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6141</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18200</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4200</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>81954</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69884</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>89963</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>104952</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>97446</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>112546</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87980</t>
+          <t>75244</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74865</t>
+          <t>68320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96274</t>
+          <t>80257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>192932</t>
+          <t>157197</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177431</t>
+          <t>141310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205755</t>
+          <t>167252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10849</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8049</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4343</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2856</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3051</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4784</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>7818</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10395</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>17085</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>6152</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11602</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>70367</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>62547</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>77211</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>84172</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>77829</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>89529</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>81,27%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>87746</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82644</t>
+          <t>92547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>159912</t>
+          <t>158113</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150450</t>
+          <t>148266</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167661</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17694</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>9440</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>31362</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>10806</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>17662</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47243</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>44337</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>33724</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>58156</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>15577</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81402</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>338269</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>320413</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>352690</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>76,29%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>318780</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>306785</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>332663</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>353931</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>332203</t>
+          <t>288634</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>370907</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>672711</t>
+          <t>640096</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>647219</t>
+          <t>619358</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>695108</t>
+          <t>660123</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
